--- a/data/import-template.xlsx
+++ b/data/import-template.xlsx
@@ -7,9 +7,10 @@
     <sheet sheetId="1" name="Instructions" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Sites" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="Radars" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Site_Activities" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Sources" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="Contacts" state="visible" r:id="rId9"/>
+    <sheet sheetId="4" name="Systems" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Site_Activities" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Sources" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="Contacts" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -193,7 +194,7 @@
     <comment ref="A1" authorId="0">
       <text>
         <r>
-          <t>activity_id is REQUIRED.</t>
+          <t>system_id is REQUIRED.</t>
         </r>
       </text>
     </comment>
@@ -207,31 +208,39 @@
     <comment ref="C1" authorId="0">
       <text>
         <r>
-          <t xml:space="preserve">activity_category is REQUIRED.
-Allowed values: Missile Test, Space Launch, Radar Tracking, Telemetry, Missile Defense, Range Safety, Aerospace Test, Other</t>
+          <t>system_name is REQUIRED.</t>
         </r>
       </text>
     </comment>
     <comment ref="D1" authorId="0">
       <text>
         <r>
-          <t>activity_description is REQUIRED.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">status is REQUIRED.
-Allowed values: Current, Historical, Planned, Unknown</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="0">
+          <t xml:space="preserve">system_category is REQUIRED.
+Allowed values: Optical Tracking, Telemetry / Range Safety, Electronic Warfare, Communications, Command &amp; Control, Test Instrumentation, Weapons Test, Other</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">operational_status is REQUIRED.
+Allowed values: Active, Inactive, Historical, Unknown</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">confidence_level is REQUIRED.
 Allowed values: High, Medium, Low</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">record_status is REQUIRED.
+Allowed values: Draft, Verified, Needs Review, Published, Archived</t>
         </r>
       </text>
     </comment>
@@ -248,29 +257,45 @@
     <comment ref="A1" authorId="0">
       <text>
         <r>
-          <t>source_id is REQUIRED.</t>
+          <t>activity_id is REQUIRED.</t>
         </r>
       </text>
     </comment>
     <comment ref="B1" authorId="0">
       <text>
         <r>
-          <t>source_title is REQUIRED.</t>
+          <t>site_id is REQUIRED.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">activity_category is REQUIRED.
+Allowed values: Missile Test, Space Launch, Radar Tracking, Telemetry, Missile Defense, Range Safety, Aerospace Test, Other</t>
         </r>
       </text>
     </comment>
     <comment ref="D1" authorId="0">
       <text>
         <r>
-          <t xml:space="preserve">source_type is REQUIRED.
-Allowed values: Official, Government, Contractor, News, Academic, Industry, Other</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0">
-      <text>
-        <r>
-          <t>access_date is REQUIRED.</t>
+          <t>activity_description is REQUIRED.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">status is REQUIRED.
+Allowed values: Current, Historical, Planned, Unknown</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">confidence_level is REQUIRED.
+Allowed values: High, Medium, Low</t>
         </r>
       </text>
     </comment>
@@ -287,6 +312,45 @@
     <comment ref="A1" authorId="0">
       <text>
         <r>
+          <t>source_id is REQUIRED.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <t>source_title is REQUIRED.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">source_type is REQUIRED.
+Allowed values: Official, Government, Contractor, News, Academic, Industry, Other</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <t>access_date is REQUIRED.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
           <t>contact_id is REQUIRED.</t>
         </r>
       </text>
@@ -318,7 +382,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="173">
   <si>
     <t>LAPAM Ranges App — Import Template</t>
   </si>
@@ -341,6 +405,9 @@
     <t xml:space="preserve">  • Radars            — radars installed at a Site (Radars.site_id must exist in Sites)</t>
   </si>
   <si>
+    <t xml:space="preserve">  • Systems           — non-radar instrumentation: optical tracking, telemetry, EW, C2, etc.</t>
+  </si>
+  <si>
     <t xml:space="preserve">  • Site_Activities   — operational/historical activities at a Site</t>
   </si>
   <si>
@@ -648,6 +715,66 @@
   </si>
   <si>
     <t>U.S. Army FOIA release (2024)</t>
+  </si>
+  <si>
+    <t>system_id</t>
+  </si>
+  <si>
+    <t>system_name</t>
+  </si>
+  <si>
+    <t>system_category</t>
+  </si>
+  <si>
+    <t>SYS-0001-001</t>
+  </si>
+  <si>
+    <t>Optical tracking systems and kinetheodolites</t>
+  </si>
+  <si>
+    <t>Optical Tracking</t>
+  </si>
+  <si>
+    <t>Optical trajectory measurement, separation and impact imaging</t>
+  </si>
+  <si>
+    <t>Swedish Defence Materiel Administration (FMV)</t>
+  </si>
+  <si>
+    <t>FMV Test &amp; Evaluation, Vidsel</t>
+  </si>
+  <si>
+    <t>Not publicly disclosed</t>
+  </si>
+  <si>
+    <t>FMV lists optical tracking systems as current Vidsel instrumentation.</t>
+  </si>
+  <si>
+    <t>2026-06-13</t>
+  </si>
+  <si>
+    <t>SRC-0002</t>
+  </si>
+  <si>
+    <t>SRC-0002, SRC-0014</t>
+  </si>
+  <si>
+    <t>SYS-0001-002</t>
+  </si>
+  <si>
+    <t>Telemetry ground systems and Flight Termination</t>
+  </si>
+  <si>
+    <t>Telemetry / Range Safety</t>
+  </si>
+  <si>
+    <t>Receive onboard test data and support range-safety flight termination</t>
+  </si>
+  <si>
+    <t>FMV's current capability page lists telemetry and a Flight Termination system.</t>
+  </si>
+  <si>
+    <t>SRC-0002, SRC-0016</t>
   </si>
   <si>
     <t>activity_id</t>
@@ -1203,7 +1330,7 @@
   <sheetPr>
     <tabColor rgb="FF3B82F6"/>
   </sheetPr>
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
@@ -1266,16 +1393,16 @@
     </row>
     <row r="12" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
     <row r="14" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="4" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1311,16 +1438,16 @@
     </row>
     <row r="21" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
     <row r="23" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1341,12 +1468,17 @@
     </row>
     <row r="27" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
-        <v>23</v>
+    <row r="29" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1381,96 +1513,96 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:23" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q1" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="R1" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="S1" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T1" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="U1" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="V1" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="W1" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E2">
         <v>95</v>
       </c>
       <c r="F2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H2">
         <v>32.395</v>
@@ -1479,69 +1611,69 @@
         <v>-106.483</v>
       </c>
       <c r="J2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Q2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="S2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="T2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="U2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="V2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E3">
         <v>92</v>
       </c>
       <c r="F3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H3">
         <v>34.742</v>
@@ -1550,46 +1682,46 @@
         <v>-120.572</v>
       </c>
       <c r="J3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="U3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="3:22" x14ac:dyDescent="0.25"/>
@@ -1853,123 +1985,123 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q1" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="R1" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="S1" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="T1" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="R2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="S2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="T2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="5:19" x14ac:dyDescent="0.25"/>
@@ -2206,6 +2338,398 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:O201"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="36" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="40" customWidth="1"/>
+    <col min="6" max="7" width="26" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="10" max="10" width="48" customWidth="1"/>
+    <col min="11" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="14" max="14" width="24" customWidth="1"/>
+    <col min="15" max="15" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I2" t="s">
+        <v>107</v>
+      </c>
+      <c r="J2" t="s">
+        <v>121</v>
+      </c>
+      <c r="K2" t="s">
+        <v>64</v>
+      </c>
+      <c r="L2" t="s">
+        <v>122</v>
+      </c>
+      <c r="M2" t="s">
+        <v>123</v>
+      </c>
+      <c r="N2" t="s">
+        <v>124</v>
+      </c>
+      <c r="O2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F3" t="s">
+        <v>118</v>
+      </c>
+      <c r="G3" t="s">
+        <v>119</v>
+      </c>
+      <c r="H3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I3" t="s">
+        <v>107</v>
+      </c>
+      <c r="J3" t="s">
+        <v>129</v>
+      </c>
+      <c r="K3" t="s">
+        <v>64</v>
+      </c>
+      <c r="L3" t="s">
+        <v>122</v>
+      </c>
+      <c r="M3" t="s">
+        <v>123</v>
+      </c>
+      <c r="N3" t="s">
+        <v>130</v>
+      </c>
+      <c r="O3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="65" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="81" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="97" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="98" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="100" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="101" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="102" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="104" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="105" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="106" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="107" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="108" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="109" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="110" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="111" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="112" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="113" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="114" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="115" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="116" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="117" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="118" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="119" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="120" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="121" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="122" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="123" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="124" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="125" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="126" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="127" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="128" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="129" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="130" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="131" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="132" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="133" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="134" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="135" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="136" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="137" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="138" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="139" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="140" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="141" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="142" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="143" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="144" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="145" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="146" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="147" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="148" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="149" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="150" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="151" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="152" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="153" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="154" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="155" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="156" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="157" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="158" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="159" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="160" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="161" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="162" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="163" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="164" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="165" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="166" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="167" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="168" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="169" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="170" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="171" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="172" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="173" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="174" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="175" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="176" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="177" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="178" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="179" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="180" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="181" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="182" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="183" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="184" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="185" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="186" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="187" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="188" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="189" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="190" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="191" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="192" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="193" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="194" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="195" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="196" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="197" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="198" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="199" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="200" spans="4:15" x14ac:dyDescent="0.25"/>
+    <row r="201" spans="4:15" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <dataValidations count="8">
+    <dataValidation type="list" showErrorMessage="1" errorStyle="stop" errorTitle="Invalid value" error="Must be one of: Optical Tracking, Telemetry / Range Safety, Electronic Warfare, Communications, Command &amp; Control, Test Instrumentation, Weapons Test, Other" sqref="D10:D201">
+      <formula1>"Optical Tracking,Telemetry / Range Safety,Electronic Warfare,Communications,Command &amp; Control,Test Instrumentation,Weapons Test,Other"</formula1>
+    </dataValidation>
+    <dataValidation type="list" showErrorMessage="1" errorStyle="stop" errorTitle="Invalid value" error="Must be one of: Optical Tracking, Telemetry / Range Safety, Electronic Warfare, Communications, Command &amp; Control, Test Instrumentation, Weapons Test, Other" sqref="D2:D201">
+      <formula1>"Optical Tracking,Telemetry / Range Safety,Electronic Warfare,Communications,Command &amp; Control,Test Instrumentation,Weapons Test,Other"</formula1>
+    </dataValidation>
+    <dataValidation type="list" showErrorMessage="1" errorStyle="stop" errorTitle="Invalid value" error="Must be one of: Active, Inactive, Historical, Unknown" sqref="I10:I201">
+      <formula1>"Active,Inactive,Historical,Unknown"</formula1>
+    </dataValidation>
+    <dataValidation type="list" showErrorMessage="1" errorStyle="stop" errorTitle="Invalid value" error="Must be one of: Active, Inactive, Historical, Unknown" sqref="I2:I201">
+      <formula1>"Active,Inactive,Historical,Unknown"</formula1>
+    </dataValidation>
+    <dataValidation type="list" showErrorMessage="1" errorStyle="stop" errorTitle="Invalid value" error="Must be one of: High, Medium, Low" sqref="K10:K201">
+      <formula1>"High,Medium,Low"</formula1>
+    </dataValidation>
+    <dataValidation type="list" showErrorMessage="1" errorStyle="stop" errorTitle="Invalid value" error="Must be one of: High, Medium, Low" sqref="K2:K201">
+      <formula1>"High,Medium,Low"</formula1>
+    </dataValidation>
+    <dataValidation type="list" showErrorMessage="1" errorStyle="stop" errorTitle="Invalid value" error="Must be one of: Draft, Verified, Needs Review, Published, Archived" sqref="O10:O201">
+      <formula1>"Draft,Verified,Needs Review,Published,Archived"</formula1>
+    </dataValidation>
+    <dataValidation type="list" showErrorMessage="1" errorStyle="stop" errorTitle="Invalid value" error="Must be one of: Draft, Verified, Needs Review, Published, Archived" sqref="O2:O201">
+      <formula1>"Draft,Verified,Needs Review,Published,Archived"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J201"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -2220,51 +2744,51 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C2" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="D2" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="E2" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="F2">
         <v>2003</v>
@@ -2273,30 +2797,30 @@
         <v>2025</v>
       </c>
       <c r="H2" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="I2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="D3" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="E3" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="F3">
         <v>2021</v>
@@ -2305,13 +2829,13 @@
         <v>2026</v>
       </c>
       <c r="H3" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="I3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="3:10" x14ac:dyDescent="0.25"/>
@@ -2539,7 +3063,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J201"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -2556,63 +3080,63 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B2" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="C2" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="D2" t="s">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="E2" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="F2" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="G2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H2">
         <v>95</v>
       </c>
       <c r="I2" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="J2" t="s">
         <v>1</v>
@@ -2832,7 +3356,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I201"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -2848,60 +3372,60 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C2" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="D2" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="E2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G2" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="H2" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="I2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="4:4" x14ac:dyDescent="0.25"/>

--- a/data/import-template.xlsx
+++ b/data/import-template.xlsx
@@ -7,10 +7,11 @@
     <sheet sheetId="1" name="Instructions" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Sites" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="Radars" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Systems" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Site_Activities" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="Sources" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Contacts" state="visible" r:id="rId10"/>
+    <sheet sheetId="4" name="Radar_Lifecycle" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Systems" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Site_Activities" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="Sources" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="Contacts" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -194,53 +195,37 @@
     <comment ref="A1" authorId="0">
       <text>
         <r>
-          <t>system_id is REQUIRED.</t>
+          <t>event_id is REQUIRED.</t>
         </r>
       </text>
     </comment>
     <comment ref="B1" authorId="0">
       <text>
         <r>
+          <t>radar_id is REQUIRED.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
           <t>site_id is REQUIRED.</t>
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0">
-      <text>
-        <r>
-          <t>system_name is REQUIRED.</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="D1" authorId="0">
       <text>
         <r>
-          <t xml:space="preserve">system_category is REQUIRED.
-Allowed values: Optical Tracking, Telemetry / Range Safety, Electronic Warfare, Communications, Command &amp; Control, Test Instrumentation, Weapons Test, Other</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">operational_status is REQUIRED.
-Allowed values: Active, Inactive, Historical, Unknown</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">confidence_level is REQUIRED.
-Allowed values: High, Medium, Low</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O1" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">record_status is REQUIRED.
-Allowed values: Draft, Verified, Needs Review, Published, Archived</t>
+          <t xml:space="preserve">event_type is REQUIRED.
+Allowed values: Procurement specification, Procurement award, Contract award, Delivery / modernization, Acceptance, Commissioning, Planned acquisition, Historical reference, Decommissioning, Other</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">
+Allowed values: USD, EUR, SEK, NOK, DKK, GBP, ILS, JPY, Other</t>
         </r>
       </text>
     </comment>
@@ -257,7 +242,7 @@
     <comment ref="A1" authorId="0">
       <text>
         <r>
-          <t>activity_id is REQUIRED.</t>
+          <t>system_id is REQUIRED.</t>
         </r>
       </text>
     </comment>
@@ -271,31 +256,39 @@
     <comment ref="C1" authorId="0">
       <text>
         <r>
-          <t xml:space="preserve">activity_category is REQUIRED.
-Allowed values: Missile Test, Space Launch, Radar Tracking, Telemetry, Missile Defense, Range Safety, Aerospace Test, Other</t>
+          <t>system_name is REQUIRED.</t>
         </r>
       </text>
     </comment>
     <comment ref="D1" authorId="0">
       <text>
         <r>
-          <t>activity_description is REQUIRED.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">status is REQUIRED.
-Allowed values: Current, Historical, Planned, Unknown</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="0">
+          <t xml:space="preserve">system_category is REQUIRED.
+Allowed values: Optical Tracking, Telemetry / Range Safety, Electronic Warfare, Communications, Command &amp; Control, Test Instrumentation, Weapons Test, Other</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">operational_status is REQUIRED.
+Allowed values: Active, Inactive, Historical, Unknown</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">confidence_level is REQUIRED.
 Allowed values: High, Medium, Low</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">record_status is REQUIRED.
+Allowed values: Draft, Verified, Needs Review, Published, Archived</t>
         </r>
       </text>
     </comment>
@@ -312,29 +305,45 @@
     <comment ref="A1" authorId="0">
       <text>
         <r>
-          <t>source_id is REQUIRED.</t>
+          <t>activity_id is REQUIRED.</t>
         </r>
       </text>
     </comment>
     <comment ref="B1" authorId="0">
       <text>
         <r>
-          <t>source_title is REQUIRED.</t>
+          <t>site_id is REQUIRED.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">activity_category is REQUIRED.
+Allowed values: Missile Test, Space Launch, Radar Tracking, Telemetry, Missile Defense, Range Safety, Aerospace Test, Other</t>
         </r>
       </text>
     </comment>
     <comment ref="D1" authorId="0">
       <text>
         <r>
-          <t xml:space="preserve">source_type is REQUIRED.
-Allowed values: Official, Government, Contractor, News, Academic, Industry, Other</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0">
-      <text>
-        <r>
-          <t>access_date is REQUIRED.</t>
+          <t>activity_description is REQUIRED.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">status is REQUIRED.
+Allowed values: Current, Historical, Planned, Unknown</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">confidence_level is REQUIRED.
+Allowed values: High, Medium, Low</t>
         </r>
       </text>
     </comment>
@@ -351,6 +360,45 @@
     <comment ref="A1" authorId="0">
       <text>
         <r>
+          <t>source_id is REQUIRED.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <t>source_title is REQUIRED.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">source_type is REQUIRED.
+Allowed values: Official, Government, Contractor, News, Academic, Industry, Other</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <t>access_date is REQUIRED.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
           <t>contact_id is REQUIRED.</t>
         </r>
       </text>
@@ -382,7 +430,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="212">
   <si>
     <t>LAPAM Ranges App — Import Template</t>
   </si>
@@ -405,6 +453,9 @@
     <t xml:space="preserve">  • Radars            — radars installed at a Site (Radars.site_id must exist in Sites)</t>
   </si>
   <si>
+    <t xml:space="preserve">  • Radar_Lifecycle   — procurement / contract / delivery / acceptance / decommissioning events per Radar</t>
+  </si>
+  <si>
     <t xml:space="preserve">  • Systems           — non-radar instrumentation: optical tracking, telemetry, EW, C2, etc.</t>
   </si>
   <si>
@@ -715,6 +766,120 @@
   </si>
   <si>
     <t>U.S. Army FOIA release (2024)</t>
+  </si>
+  <si>
+    <t>event_id</t>
+  </si>
+  <si>
+    <t>event_type</t>
+  </si>
+  <si>
+    <t>event_date</t>
+  </si>
+  <si>
+    <t>event_year</t>
+  </si>
+  <si>
+    <t>event_title</t>
+  </si>
+  <si>
+    <t>event_description</t>
+  </si>
+  <si>
+    <t>authority_or_owner</t>
+  </si>
+  <si>
+    <t>supplier_or_contractor</t>
+  </si>
+  <si>
+    <t>disclosed_value</t>
+  </si>
+  <si>
+    <t>currency</t>
+  </si>
+  <si>
+    <t>value_scope</t>
+  </si>
+  <si>
+    <t>evidence_status</t>
+  </si>
+  <si>
+    <t>source_ids</t>
+  </si>
+  <si>
+    <t>analyst_note</t>
+  </si>
+  <si>
+    <t>EVT-RAD-0137-001</t>
+  </si>
+  <si>
+    <t>RAD-0137-001</t>
+  </si>
+  <si>
+    <t>SITE-0137</t>
+  </si>
+  <si>
+    <t>Procurement award</t>
+  </si>
+  <si>
+    <t>2018-02-23</t>
+  </si>
+  <si>
+    <t>Reported FMV award for radar with optical tracking</t>
+  </si>
+  <si>
+    <t>A procurement mirror reports award UH-2017-39 to Weibel including delivery of optical-precision tracking systems for the Vidsel range.</t>
+  </si>
+  <si>
+    <t>FMV</t>
+  </si>
+  <si>
+    <t>Weibel Scientific A/S</t>
+  </si>
+  <si>
+    <t>195583823</t>
+  </si>
+  <si>
+    <t>SEK</t>
+  </si>
+  <si>
+    <t>Mirror-reported total contract value including peripherals.</t>
+  </si>
+  <si>
+    <t>Reported by procurement mirror; Confirmed by official FMV release.</t>
+  </si>
+  <si>
+    <t>SRC-0006</t>
+  </si>
+  <si>
+    <t>The award date must not be entered as the installation or commissioning date.</t>
+  </si>
+  <si>
+    <t>EVT-RAD-0137-002</t>
+  </si>
+  <si>
+    <t>Delivery / modernization</t>
+  </si>
+  <si>
+    <t>First of two combined radar-optical precision systems received</t>
+  </si>
+  <si>
+    <t>FMV reported receipt of the first of two mobile systems combining radar and optical precision tracking in 2021.</t>
+  </si>
+  <si>
+    <t>&gt;100000000</t>
+  </si>
+  <si>
+    <t>FMV's published 2021 investment in Vidsel FMV radar systems and new test capabilities.</t>
+  </si>
+  <si>
+    <t>Confirmed by official FMV and manufacturer sources.</t>
+  </si>
+  <si>
+    <t>SRC-0014, SRC-0015</t>
+  </si>
+  <si>
+    <t>Exact model designation, exact commissioning date, and cost allocated to the system not disclosed publicly.</t>
   </si>
   <si>
     <t>system_id</t>
@@ -1330,7 +1495,7 @@
   <sheetPr>
     <tabColor rgb="FF3B82F6"/>
   </sheetPr>
-  <dimension ref="A1:A29"/>
+  <dimension ref="A1:A30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
@@ -1398,16 +1563,16 @@
     </row>
     <row r="13" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
     <row r="15" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1443,16 +1608,16 @@
     </row>
     <row r="22" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
     <row r="24" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="4" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1473,12 +1638,17 @@
     </row>
     <row r="28" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
-        <v>24</v>
+    <row r="30" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1513,96 +1683,96 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:23" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q1" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R1" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S1" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="T1" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="U1" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="V1" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W1" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E2">
         <v>95</v>
       </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H2">
         <v>32.395</v>
@@ -1611,69 +1781,69 @@
         <v>-106.483</v>
       </c>
       <c r="J2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="V2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="W2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E3">
         <v>92</v>
       </c>
       <c r="F3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H3">
         <v>34.742</v>
@@ -1682,46 +1852,46 @@
         <v>-120.572</v>
       </c>
       <c r="J3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="N3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="S3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="W3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="3:22" x14ac:dyDescent="0.25"/>
@@ -1985,123 +2155,123 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q1" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R1" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="S1" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T1" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Q2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="R2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="S2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="T2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="5:19" x14ac:dyDescent="0.25"/>
@@ -2338,6 +2508,397 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:P201"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="7" max="7" width="36" customWidth="1"/>
+    <col min="8" max="8" width="48" customWidth="1"/>
+    <col min="9" max="10" width="26" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="13" max="13" width="36" customWidth="1"/>
+    <col min="14" max="14" width="28" customWidth="1"/>
+    <col min="15" max="15" width="24" customWidth="1"/>
+    <col min="16" max="16" width="36" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F2">
+        <v>2018</v>
+      </c>
+      <c r="G2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H2" t="s">
+        <v>132</v>
+      </c>
+      <c r="I2" t="s">
+        <v>133</v>
+      </c>
+      <c r="J2" t="s">
+        <v>134</v>
+      </c>
+      <c r="K2" t="s">
+        <v>135</v>
+      </c>
+      <c r="L2" t="s">
+        <v>136</v>
+      </c>
+      <c r="M2" t="s">
+        <v>137</v>
+      </c>
+      <c r="N2" t="s">
+        <v>138</v>
+      </c>
+      <c r="O2" t="s">
+        <v>139</v>
+      </c>
+      <c r="P2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D3" t="s">
+        <v>142</v>
+      </c>
+      <c r="E3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>2021</v>
+      </c>
+      <c r="G3" t="s">
+        <v>143</v>
+      </c>
+      <c r="H3" t="s">
+        <v>144</v>
+      </c>
+      <c r="I3" t="s">
+        <v>133</v>
+      </c>
+      <c r="J3" t="s">
+        <v>134</v>
+      </c>
+      <c r="K3" t="s">
+        <v>145</v>
+      </c>
+      <c r="L3" t="s">
+        <v>136</v>
+      </c>
+      <c r="M3" t="s">
+        <v>146</v>
+      </c>
+      <c r="N3" t="s">
+        <v>147</v>
+      </c>
+      <c r="O3" t="s">
+        <v>148</v>
+      </c>
+      <c r="P3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="4" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="65" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="81" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="97" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="98" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="100" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="101" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="102" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="104" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="105" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="106" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="107" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="108" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="109" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="110" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="111" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="112" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="113" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="114" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="115" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="116" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="117" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="118" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="119" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="120" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="121" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="122" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="123" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="124" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="125" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="126" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="127" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="128" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="129" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="130" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="131" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="132" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="133" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="134" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="135" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="136" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="137" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="138" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="139" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="140" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="141" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="142" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="143" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="144" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="145" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="146" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="147" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="148" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="149" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="150" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="151" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="152" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="153" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="154" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="155" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="156" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="157" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="158" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="159" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="160" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="161" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="162" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="163" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="164" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="165" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="166" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="167" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="168" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="169" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="170" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="171" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="172" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="173" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="174" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="175" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="176" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="177" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="178" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="179" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="180" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="181" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="182" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="183" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="184" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="185" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="186" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="187" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="188" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="189" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="190" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="191" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="192" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="193" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="194" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="195" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="196" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="197" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="198" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="199" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="200" spans="4:12" x14ac:dyDescent="0.25"/>
+    <row r="201" spans="4:12" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <dataValidations count="4">
+    <dataValidation type="list" showErrorMessage="1" errorStyle="stop" errorTitle="Invalid value" error="Must be one of: Procurement specification, Procurement award, Contract award, Delivery / modernization, Acceptance, Commissioning, Planned acquisition, Historical reference, Decommissioning, Other" sqref="D10:D201">
+      <formula1>"Procurement specification,Procurement award,Contract award,Delivery / modernization,Acceptance,Commissioning,Planned acquisition,Historical reference,Decommissioning,Other"</formula1>
+    </dataValidation>
+    <dataValidation type="list" showErrorMessage="1" errorStyle="stop" errorTitle="Invalid value" error="Must be one of: Procurement specification, Procurement award, Contract award, Delivery / modernization, Acceptance, Commissioning, Planned acquisition, Historical reference, Decommissioning, Other" sqref="D2:D201">
+      <formula1>"Procurement specification,Procurement award,Contract award,Delivery / modernization,Acceptance,Commissioning,Planned acquisition,Historical reference,Decommissioning,Other"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Invalid value" error="Must be one of: USD, EUR, SEK, NOK, DKK, GBP, ILS, JPY, Other" sqref="L10:L201">
+      <formula1>"USD,EUR,SEK,NOK,DKK,GBP,ILS,JPY,Other"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Invalid value" error="Must be one of: USD, EUR, SEK, NOK, DKK, GBP, ILS, JPY, Other" sqref="L2:L201">
+      <formula1>"USD,EUR,SEK,NOK,DKK,GBP,ILS,JPY,Other"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O201"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -2358,143 +2919,143 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>111</v>
+        <v>150</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>113</v>
+        <v>152</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N1" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="O1" s="7" t="s">
         <v>47</v>
-      </c>
-      <c r="O1" s="7" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>115</v>
+        <v>154</v>
       </c>
       <c r="D2" t="s">
-        <v>116</v>
+        <v>155</v>
       </c>
       <c r="E2" t="s">
-        <v>117</v>
+        <v>156</v>
       </c>
       <c r="F2" t="s">
-        <v>118</v>
+        <v>157</v>
       </c>
       <c r="G2" t="s">
-        <v>119</v>
+        <v>158</v>
       </c>
       <c r="H2" t="s">
-        <v>120</v>
+        <v>159</v>
       </c>
       <c r="I2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J2" t="s">
-        <v>121</v>
+        <v>160</v>
       </c>
       <c r="K2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L2" t="s">
-        <v>122</v>
+        <v>161</v>
       </c>
       <c r="M2" t="s">
-        <v>123</v>
+        <v>162</v>
       </c>
       <c r="N2" t="s">
-        <v>124</v>
+        <v>163</v>
       </c>
       <c r="O2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>125</v>
+        <v>164</v>
       </c>
       <c r="B3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>126</v>
+        <v>165</v>
       </c>
       <c r="D3" t="s">
-        <v>127</v>
+        <v>166</v>
       </c>
       <c r="E3" t="s">
-        <v>128</v>
+        <v>167</v>
       </c>
       <c r="F3" t="s">
-        <v>118</v>
+        <v>157</v>
       </c>
       <c r="G3" t="s">
-        <v>119</v>
+        <v>158</v>
       </c>
       <c r="H3" t="s">
-        <v>120</v>
+        <v>159</v>
       </c>
       <c r="I3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J3" t="s">
-        <v>129</v>
+        <v>168</v>
       </c>
       <c r="K3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L3" t="s">
-        <v>122</v>
+        <v>161</v>
       </c>
       <c r="M3" t="s">
-        <v>123</v>
+        <v>162</v>
       </c>
       <c r="N3" t="s">
-        <v>130</v>
+        <v>169</v>
       </c>
       <c r="O3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="4:15" x14ac:dyDescent="0.25"/>
@@ -2728,7 +3289,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J201"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -2744,51 +3305,51 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>131</v>
+        <v>170</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>132</v>
+        <v>171</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>133</v>
+        <v>172</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>134</v>
+        <v>173</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>135</v>
+        <v>174</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>136</v>
+        <v>175</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>137</v>
+        <v>176</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>138</v>
+        <v>177</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="D2" t="s">
-        <v>140</v>
+        <v>179</v>
       </c>
       <c r="E2" t="s">
-        <v>141</v>
+        <v>180</v>
       </c>
       <c r="F2">
         <v>2003</v>
@@ -2797,30 +3358,30 @@
         <v>2025</v>
       </c>
       <c r="H2" t="s">
-        <v>142</v>
+        <v>181</v>
       </c>
       <c r="I2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>143</v>
+        <v>182</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>144</v>
+        <v>183</v>
       </c>
       <c r="D3" t="s">
-        <v>145</v>
+        <v>184</v>
       </c>
       <c r="E3" t="s">
-        <v>146</v>
+        <v>185</v>
       </c>
       <c r="F3">
         <v>2021</v>
@@ -2829,13 +3390,13 @@
         <v>2026</v>
       </c>
       <c r="H3" t="s">
-        <v>142</v>
+        <v>181</v>
       </c>
       <c r="I3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="3:10" x14ac:dyDescent="0.25"/>
@@ -3063,7 +3624,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J201"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -3080,63 +3641,63 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>148</v>
+        <v>187</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>149</v>
+        <v>188</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>150</v>
+        <v>189</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>151</v>
+        <v>190</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>152</v>
+        <v>191</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>153</v>
+        <v>192</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>154</v>
+        <v>193</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>155</v>
+        <v>194</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B2" t="s">
-        <v>156</v>
+        <v>195</v>
       </c>
       <c r="C2" t="s">
-        <v>157</v>
+        <v>196</v>
       </c>
       <c r="D2" t="s">
-        <v>158</v>
+        <v>197</v>
       </c>
       <c r="E2" t="s">
-        <v>159</v>
+        <v>198</v>
       </c>
       <c r="F2" t="s">
-        <v>160</v>
+        <v>199</v>
       </c>
       <c r="G2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H2">
         <v>95</v>
       </c>
       <c r="I2" t="s">
-        <v>161</v>
+        <v>200</v>
       </c>
       <c r="J2" t="s">
         <v>1</v>
@@ -3356,7 +3917,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I201"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -3372,60 +3933,60 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>162</v>
+        <v>201</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>163</v>
+        <v>202</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>164</v>
+        <v>203</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>165</v>
+        <v>204</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>166</v>
+        <v>205</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>167</v>
+        <v>206</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>154</v>
+        <v>193</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>168</v>
+        <v>207</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="D2" t="s">
-        <v>170</v>
+        <v>209</v>
       </c>
       <c r="E2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G2" t="s">
-        <v>171</v>
+        <v>210</v>
       </c>
       <c r="H2" t="s">
-        <v>172</v>
+        <v>211</v>
       </c>
       <c r="I2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="4:4" x14ac:dyDescent="0.25"/>
